--- a/public/downloads/planilha-precificacao-barbearia.xlsx
+++ b/public/downloads/planilha-precificacao-barbearia.xlsx
@@ -8,16 +8,18 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Leia primeiro" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Custos" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Precificação" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Comece aqui" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Painel rápido" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Custos" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Precificação" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Custos!$A$1:$C$10</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Leia primeiro'!$A$1:$F$16</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Precificação!$A$1:$I$21</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Precificação!$A$1:$I$21</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Precificação!A1:I21</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Comece aqui'!$A$1:$F$19</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Custos!$A$1:$C$10</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Painel rápido'!$A$1:$I$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Precificação!$A$1:$I$21</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Precificação!$A$1:$I$21</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Precificação!A1:I21</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
-  <si>
-    <t xml:space="preserve">MATERIAL PRÁTICO FLOWO</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+  <si>
+    <t xml:space="preserve">FLOWO · MATERIAL PRÁTICO</t>
   </si>
   <si>
     <t xml:space="preserve">Planilha de precificação de serviços</t>
@@ -40,19 +42,46 @@
     <t xml:space="preserve">Organize custos, capacidade e margem para tomar decisões de preço com mais clareza.</t>
   </si>
   <si>
-    <t xml:space="preserve">flowo.com.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMO USAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Substitua os custos e a capacidade produtiva mensal pelos dados da barbearia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Revise insumos e tempo de cada serviço.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Compare preço calculado, mercado e posicionamento antes de decidir.</t>
+    <t xml:space="preserve">Veja o resumo na próxima aba. Depois, preencha somente as células rosadas e volte ao resumo para decidir o que fazer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troque os custos e as horas de atendimento pelos números da barbearia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revise material usado e tempo de cada serviço.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare o preço calculado com o preço praticado na sua região.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEGENDA RÁPIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIGITE AQUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESULTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATENÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Células rosadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Células verdes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Células amarelas</t>
   </si>
   <si>
     <t xml:space="preserve">ANTES DE COMEÇAR</t>
@@ -70,6 +99,54 @@
     <t xml:space="preserve">Material educativo. Adapte à realidade da sua barbearia e valide decisões contábeis, fiscais, trabalhistas e jurídicas com profissionais habilitados.</t>
   </si>
   <si>
+    <t xml:space="preserve">flowo.com.br/recursos/materiais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOWO · RESUMO SIMPLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seu preço precisa caber na rotina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use o cálculo como referência e compare com mercado, posicionamento e capacidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVIÇOS PREENCHIDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREÇO CALCULADO MÉDIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREÇOS FINAIS DEFINIDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">serviços com nome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">referência dos serviços cadastrados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decisões já registradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRÓXIMA AÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comece por um único serviço: preencha tempo, material usado e margem; depois registre o preço final que faz sentido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMO LER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Preencha as células rosadas nas outras abas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Volte aqui para conferir os números principais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Resolva primeiro o que estiver pendente ou bloqueado.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CUSTOS FIXOS MENSAIS</t>
   </si>
   <si>
@@ -124,10 +201,10 @@
     <t xml:space="preserve">Tempo (min)</t>
   </si>
   <si>
-    <t xml:space="preserve">Insumos (R$)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo fixo rateado pelo tempo</t>
+    <t xml:space="preserve">Material usado (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parte dos custos fixos</t>
   </si>
   <si>
     <t xml:space="preserve">Custo total</t>
@@ -161,13 +238,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$ &quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -200,15 +278,23 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="20"/>
+      <sz val="22"/>
       <color rgb="FF171810"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF6D6A61"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF6D6A61"/>
+      <color rgb="FF171810"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -231,13 +317,89 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color rgb="FF7A173F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F7A50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFA45D13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6D6A61"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF171810"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC52663"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6D6A61"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="22"/>
+      <color rgb="FF1F7A50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFA45D13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF171810"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7A173F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,12 +415,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F0E5"/>
-        <bgColor rgb="FFFBF9F3"/>
+        <bgColor rgb="FFFAEEDB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBF9F3"/>
+        <bgColor rgb="FFF4F0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8E9EF"/>
+        <bgColor rgb="FFF4F0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F3EC"/>
+        <bgColor rgb="FFF4F0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAEEDB"/>
         <bgColor rgb="FFF4F0E5"/>
       </patternFill>
     </fill>
@@ -312,7 +492,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -329,39 +509,71 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -369,23 +581,35 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -398,11 +622,27 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF171810"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8E9EF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7A173F"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -418,7 +658,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFBF9F3"/>
+          <fgColor rgb="FFE7F3EC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -439,14 +679,14 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF1F7A50"/>
       <rgbColor rgb="FFD9D3C6"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F0E5"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFC52663"/>
+      <rgbColor rgb="FFFAEEDB"/>
+      <rgbColor rgb="FFE7F3EC"/>
+      <rgbColor rgb="FF7A173F"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
@@ -459,8 +699,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFF8E9EF"/>
+      <rgbColor rgb="FFF4F0E5"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -478,7 +718,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF171810"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFA45D13"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -668,14 +908,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="18.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -685,7 +924,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -695,7 +934,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -706,147 +945,178 @@
       <c r="F3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="10" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
+    <row r="8" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="10" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="10" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="46" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="24">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
@@ -863,6 +1133,224 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="0" width="14.84"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="44" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <f aca="false">COUNTIF(Precificação!$A$2:$A$21,"&lt;&gt;")</f>
+        <v>5</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16" t="n">
+        <f aca="false">IFERROR(AVERAGEIF(Precificação!$G$2:$G$21,"&gt;0"),0)</f>
+        <v>69.375</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="15" t="n">
+        <f aca="false">COUNTIF(Precificação!$H$2:$H$21,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -872,113 +1360,113 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>15</v>
+      <c r="A1" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="10" t="n">
+      <c r="A2" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="22" t="n">
         <v>3200</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>17</v>
+      <c r="C2" s="21" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="12" t="n">
+      <c r="A3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="22" t="n">
         <v>800</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>17</v>
+      <c r="C3" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="22" t="n">
         <v>500</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>17</v>
+      <c r="C4" s="21" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="12" t="n">
+      <c r="A5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>21</v>
+      <c r="C5" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <v>700</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>17</v>
+      <c r="C6" s="21" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="A7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>800</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>17</v>
+      <c r="C7" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="14" t="n">
+      <c r="A8" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <f aca="false">SUM(B2:B7)</f>
         <v>18000</v>
       </c>
-      <c r="C8" s="13"/>
+      <c r="C8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="15" t="n">
+      <c r="A9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <v>320</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>26</v>
+      <c r="C9" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <f aca="false">IFERROR(B8/(B9*60),0)</f>
         <v>0.9375</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>28</v>
+      <c r="C10" s="20" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -1021,503 +1509,503 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>15</v>
+      <c r="A1" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="9" t="n">
+      <c r="A2" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="C2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="10" t="n">
+      <c r="C2" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="28" t="n">
         <f aca="false">IF(OR(A2="",B2=""),"",Custos!$B$10*B2)</f>
         <v>37.5</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="28" t="n">
         <f aca="false">IF(A2="","",C2+D2)</f>
         <v>37.5</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="28" t="n">
         <f aca="false">IFERROR(E2/(1-F2),0)</f>
         <v>75</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="9"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="11" t="n">
+      <c r="A3" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="C3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12" t="n">
+      <c r="C3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="28" t="n">
         <f aca="false">IF(OR(A3="",B3=""),"",Custos!$B$10*B3)</f>
         <v>28.125</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="28" t="n">
         <f aca="false">IF(A3="","",C3+D3)</f>
         <v>28.125</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="28" t="n">
         <f aca="false">IFERROR(E3/(1-F3),0)</f>
         <v>56.25</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="11"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="9" t="n">
+      <c r="A4" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="27" t="n">
         <v>65</v>
       </c>
-      <c r="C4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10" t="n">
+      <c r="C4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="28" t="n">
         <f aca="false">IF(OR(A4="",B4=""),"",Custos!$B$10*B4)</f>
         <v>60.9375</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="28" t="n">
         <f aca="false">IF(A4="","",C4+D4)</f>
         <v>60.9375</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="28" t="n">
         <f aca="false">IFERROR(E4/(1-F4),0)</f>
         <v>121.875</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="9"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="27"/>
     </row>
     <row r="5" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="11" t="n">
+      <c r="A5" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="28" t="n">
         <f aca="false">IF(OR(A5="",B5=""),"",Custos!$B$10*B5)</f>
         <v>18.75</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="28" t="n">
         <f aca="false">IF(A5="","",C5+D5)</f>
         <v>18.75</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="28" t="n">
         <f aca="false">IFERROR(E5/(1-F5),0)</f>
         <v>37.5</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="11"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10" t="n">
+      <c r="C6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
         <f aca="false">IF(OR(A6="",B6=""),"",Custos!$B$10*B6)</f>
         <v>28.125</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="28" t="n">
         <f aca="false">IF(A6="","",C6+D6)</f>
         <v>28.125</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="28" t="n">
         <f aca="false">IFERROR(E6/(1-F6),0)</f>
         <v>56.25</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="9"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="str">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="str">
         <f aca="false">IF(OR(A7="",B7=""),"",Custos!$B$10*B7)</f>
         <v/>
       </c>
-      <c r="E7" s="12" t="str">
+      <c r="E7" s="28" t="str">
         <f aca="false">IF(A7="","",C7+D7)</f>
         <v/>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="12" t="n">
+      <c r="F7" s="29"/>
+      <c r="G7" s="28" t="n">
         <f aca="false">IFERROR(E7/(1-F7),0)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="11"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="str">
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="str">
         <f aca="false">IF(OR(A8="",B8=""),"",Custos!$B$10*B8)</f>
         <v/>
       </c>
-      <c r="E8" s="10" t="str">
+      <c r="E8" s="28" t="str">
         <f aca="false">IF(A8="","",C8+D8)</f>
         <v/>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="10" t="n">
+      <c r="F8" s="29"/>
+      <c r="G8" s="28" t="n">
         <f aca="false">IFERROR(E8/(1-F8),0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="9"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="str">
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="str">
         <f aca="false">IF(OR(A9="",B9=""),"",Custos!$B$10*B9)</f>
         <v/>
       </c>
-      <c r="E9" s="12" t="str">
+      <c r="E9" s="28" t="str">
         <f aca="false">IF(A9="","",C9+D9)</f>
         <v/>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="12" t="n">
+      <c r="F9" s="29"/>
+      <c r="G9" s="28" t="n">
         <f aca="false">IFERROR(E9/(1-F9),0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="11"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="10" t="str">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="28" t="str">
         <f aca="false">IF(OR(A10="",B10=""),"",Custos!$B$10*B10)</f>
         <v/>
       </c>
-      <c r="E10" s="10" t="str">
+      <c r="E10" s="28" t="str">
         <f aca="false">IF(A10="","",C10+D10)</f>
         <v/>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="10" t="n">
+      <c r="F10" s="29"/>
+      <c r="G10" s="28" t="n">
         <f aca="false">IFERROR(E10/(1-F10),0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="9"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="str">
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="28" t="str">
         <f aca="false">IF(OR(A11="",B11=""),"",Custos!$B$10*B11)</f>
         <v/>
       </c>
-      <c r="E11" s="12" t="str">
+      <c r="E11" s="28" t="str">
         <f aca="false">IF(A11="","",C11+D11)</f>
         <v/>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="12" t="n">
+      <c r="F11" s="29"/>
+      <c r="G11" s="28" t="n">
         <f aca="false">IFERROR(E11/(1-F11),0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="11"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="27"/>
     </row>
     <row r="12" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10" t="str">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="28" t="str">
         <f aca="false">IF(OR(A12="",B12=""),"",Custos!$B$10*B12)</f>
         <v/>
       </c>
-      <c r="E12" s="10" t="str">
+      <c r="E12" s="28" t="str">
         <f aca="false">IF(A12="","",C12+D12)</f>
         <v/>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="10" t="n">
+      <c r="F12" s="29"/>
+      <c r="G12" s="28" t="n">
         <f aca="false">IFERROR(E12/(1-F12),0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="9"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="str">
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="28" t="str">
         <f aca="false">IF(OR(A13="",B13=""),"",Custos!$B$10*B13)</f>
         <v/>
       </c>
-      <c r="E13" s="12" t="str">
+      <c r="E13" s="28" t="str">
         <f aca="false">IF(A13="","",C13+D13)</f>
         <v/>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="12" t="n">
+      <c r="F13" s="29"/>
+      <c r="G13" s="28" t="n">
         <f aca="false">IFERROR(E13/(1-F13),0)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="11"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="10" t="str">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="28" t="str">
         <f aca="false">IF(OR(A14="",B14=""),"",Custos!$B$10*B14)</f>
         <v/>
       </c>
-      <c r="E14" s="10" t="str">
+      <c r="E14" s="28" t="str">
         <f aca="false">IF(A14="","",C14+D14)</f>
         <v/>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10" t="n">
+      <c r="F14" s="29"/>
+      <c r="G14" s="28" t="n">
         <f aca="false">IFERROR(E14/(1-F14),0)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="9"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12" t="str">
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="28" t="str">
         <f aca="false">IF(OR(A15="",B15=""),"",Custos!$B$10*B15)</f>
         <v/>
       </c>
-      <c r="E15" s="12" t="str">
+      <c r="E15" s="28" t="str">
         <f aca="false">IF(A15="","",C15+D15)</f>
         <v/>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="12" t="n">
+      <c r="F15" s="29"/>
+      <c r="G15" s="28" t="n">
         <f aca="false">IFERROR(E15/(1-F15),0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="27"/>
     </row>
     <row r="16" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="10" t="str">
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="28" t="str">
         <f aca="false">IF(OR(A16="",B16=""),"",Custos!$B$10*B16)</f>
         <v/>
       </c>
-      <c r="E16" s="10" t="str">
+      <c r="E16" s="28" t="str">
         <f aca="false">IF(A16="","",C16+D16)</f>
         <v/>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="10" t="n">
+      <c r="F16" s="29"/>
+      <c r="G16" s="28" t="n">
         <f aca="false">IFERROR(E16/(1-F16),0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="9"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="27"/>
     </row>
     <row r="17" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="12" t="str">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="28" t="str">
         <f aca="false">IF(OR(A17="",B17=""),"",Custos!$B$10*B17)</f>
         <v/>
       </c>
-      <c r="E17" s="12" t="str">
+      <c r="E17" s="28" t="str">
         <f aca="false">IF(A17="","",C17+D17)</f>
         <v/>
       </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="12" t="n">
+      <c r="F17" s="29"/>
+      <c r="G17" s="28" t="n">
         <f aca="false">IFERROR(E17/(1-F17),0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="11"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="10" t="str">
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="28" t="str">
         <f aca="false">IF(OR(A18="",B18=""),"",Custos!$B$10*B18)</f>
         <v/>
       </c>
-      <c r="E18" s="10" t="str">
+      <c r="E18" s="28" t="str">
         <f aca="false">IF(A18="","",C18+D18)</f>
         <v/>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="10" t="n">
+      <c r="F18" s="29"/>
+      <c r="G18" s="28" t="n">
         <f aca="false">IFERROR(E18/(1-F18),0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="10"/>
-      <c r="I18" s="9"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12" t="str">
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="28" t="str">
         <f aca="false">IF(OR(A19="",B19=""),"",Custos!$B$10*B19)</f>
         <v/>
       </c>
-      <c r="E19" s="12" t="str">
+      <c r="E19" s="28" t="str">
         <f aca="false">IF(A19="","",C19+D19)</f>
         <v/>
       </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="12" t="n">
+      <c r="F19" s="29"/>
+      <c r="G19" s="28" t="n">
         <f aca="false">IFERROR(E19/(1-F19),0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="11"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="10" t="str">
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="28" t="str">
         <f aca="false">IF(OR(A20="",B20=""),"",Custos!$B$10*B20)</f>
         <v/>
       </c>
-      <c r="E20" s="10" t="str">
+      <c r="E20" s="28" t="str">
         <f aca="false">IF(A20="","",C20+D20)</f>
         <v/>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="10" t="n">
+      <c r="F20" s="29"/>
+      <c r="G20" s="28" t="n">
         <f aca="false">IFERROR(E20/(1-F20),0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="9"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="27"/>
     </row>
     <row r="21" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="str">
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="28" t="str">
         <f aca="false">IF(OR(A21="",B21=""),"",Custos!$B$10*B21)</f>
         <v/>
       </c>
-      <c r="E21" s="12" t="str">
+      <c r="E21" s="28" t="str">
         <f aca="false">IF(A21="","",C21+D21)</f>
         <v/>
       </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="12" t="n">
+      <c r="F21" s="29"/>
+      <c r="G21" s="28" t="n">
         <f aca="false">IFERROR(E21/(1-F21),0)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="11"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I21"/>
